--- a/diseases/d058/2015-2019.xlsx
+++ b/diseases/d058/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>37</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.07257191320050052</v>
       </c>
@@ -1949,9 +1946,6 @@
       <c r="O10" t="n">
         <v>18</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.03530525507051377</v>
       </c>
@@ -2985,9 +2979,6 @@
       <c r="O17" t="n">
         <v>34</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.06668770402208155</v>
       </c>
@@ -4021,9 +4012,6 @@
       <c r="O24" t="n">
         <v>35</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.06864910708155454</v>
       </c>
@@ -5205,9 +5193,6 @@
       <c r="O32" t="n">
         <v>51</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.1000315560331223</v>
       </c>
@@ -6241,9 +6226,6 @@
       <c r="O39" t="n">
         <v>78</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.152989438638893</v>
       </c>
@@ -7277,9 +7259,6 @@
       <c r="O46" t="n">
         <v>41</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.08041752543839246</v>
       </c>
@@ -8461,9 +8440,6 @@
       <c r="O54" t="n">
         <v>65</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.1274911988657441</v>
       </c>
@@ -9497,9 +9473,6 @@
       <c r="O61" t="n">
         <v>151</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.296171861980421</v>
       </c>
@@ -10533,9 +10506,6 @@
       <c r="O68" t="n">
         <v>3425</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>6.71780547869498</v>
       </c>
@@ -11717,9 +11687,6 @@
       <c r="O76" t="n">
         <v>5070</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>9.944313511528042</v>
       </c>
@@ -12753,9 +12720,6 @@
       <c r="O83" t="n">
         <v>508</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.9963927542122774</v>
       </c>
@@ -13937,9 +13901,6 @@
       <c r="O91" t="n">
         <v>81</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.1579013883996166</v>
       </c>
@@ -14973,9 +14934,6 @@
       <c r="O98" t="n">
         <v>68</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.1325591902614065</v>
       </c>
@@ -16009,9 +15967,6 @@
       <c r="O105" t="n">
         <v>60</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.1169639914071234</v>
       </c>
@@ -17193,9 +17148,6 @@
       <c r="O113" t="n">
         <v>101</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1968893855353244</v>
       </c>
@@ -18229,9 +18181,6 @@
       <c r="O120" t="n">
         <v>191</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.3723353726460095</v>
       </c>
@@ -19265,9 +19214,6 @@
       <c r="O127" t="n">
         <v>202</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.3937787710706487</v>
       </c>
@@ -20449,9 +20395,6 @@
       <c r="O135" t="n">
         <v>98</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.1910411859649682</v>
       </c>
@@ -21485,9 +21428,6 @@
       <c r="O142" t="n">
         <v>96</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.1871423862513975</v>
       </c>
@@ -22521,9 +22461,6 @@
       <c r="O149" t="n">
         <v>227</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.4425137674902836</v>
       </c>
@@ -23705,9 +23642,6 @@
       <c r="O157" t="n">
         <v>2150</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>4.191209692088589</v>
       </c>
@@ -24741,9 +24675,6 @@
       <c r="O164" t="n">
         <v>7121</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>13.88167638016876</v>
       </c>
@@ -25777,9 +25708,6 @@
       <c r="O171" t="n">
         <v>710</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>1.384073898317627</v>
       </c>
@@ -26961,9 +26889,6 @@
       <c r="O179" t="n">
         <v>65</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.1262472487689704</v>
       </c>
@@ -27997,9 +27922,6 @@
       <c r="O186" t="n">
         <v>24</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.04661436877623521</v>
       </c>
@@ -29033,9 +28955,6 @@
       <c r="O193" t="n">
         <v>32</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.06215249170164695</v>
       </c>
@@ -30217,9 +30136,6 @@
       <c r="O201" t="n">
         <v>81</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.1573234946197938</v>
       </c>
@@ -31253,9 +31169,6 @@
       <c r="O208" t="n">
         <v>162</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.3146469892395877</v>
       </c>
@@ -32289,9 +32202,6 @@
       <c r="O215" t="n">
         <v>183</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.3554345619187935</v>
       </c>
@@ -33473,9 +33383,6 @@
       <c r="O223" t="n">
         <v>182</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.353492296553117</v>
       </c>
@@ -34509,9 +34416,6 @@
       <c r="O230" t="n">
         <v>171</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.3321273775306758</v>
       </c>
@@ -35693,9 +35597,6 @@
       <c r="O238" t="n">
         <v>340</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.6603702243299988</v>
       </c>
@@ -36729,9 +36630,6 @@
       <c r="O245" t="n">
         <v>3250</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>6.312362438448518</v>
       </c>
@@ -37765,9 +37663,6 @@
       <c r="O252" t="n">
         <v>5542</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>10.76403465657898</v>
       </c>
@@ -38949,9 +38844,6 @@
       <c r="O260" t="n">
         <v>496</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.9633636213755277</v>
       </c>
@@ -39985,9 +39877,6 @@
       <c r="O267" t="n">
         <v>91</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.1762169338121838</v>
       </c>
@@ -41021,9 +40910,6 @@
       <c r="O274" t="n">
         <v>41</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.07939444270658831</v>
       </c>
@@ -42057,9 +41943,6 @@
       <c r="O281" t="n">
         <v>65</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.1258692384372742</v>
       </c>
@@ -43241,9 +43124,6 @@
       <c r="O289" t="n">
         <v>169</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0.3272600199369128</v>
       </c>
@@ -44277,9 +44157,6 @@
       <c r="O296" t="n">
         <v>296</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0.5731891473451254</v>
       </c>
@@ -45461,9 +45338,6 @@
       <c r="O304" t="n">
         <v>234</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.4531292583741869</v>
       </c>
@@ -46497,9 +46371,6 @@
       <c r="O311" t="n">
         <v>232</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.4492563587299631</v>
       </c>
@@ -47533,9 +47404,6 @@
       <c r="O318" t="n">
         <v>133</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.257547826340884</v>
       </c>
@@ -48717,9 +48585,6 @@
       <c r="O326" t="n">
         <v>193</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.3737348156675986</v>
       </c>
@@ -49753,9 +49618,6 @@
       <c r="O333" t="n">
         <v>1908</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>3.694746260589524</v>
       </c>
@@ -50789,9 +50651,6 @@
       <c r="O340" t="n">
         <v>2995</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>5.79966721722517</v>
       </c>
@@ -51973,9 +51832,6 @@
       <c r="O348" t="n">
         <v>311</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.6022358946768041</v>
       </c>
@@ -53009,9 +52865,6 @@
       <c r="O355" t="n">
         <v>49</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.09465334910786129</v>
       </c>
@@ -54193,9 +54046,6 @@
       <c r="O363" t="n">
         <v>33</v>
       </c>
-      <c r="Q363" t="n">
-        <v>0</v>
-      </c>
       <c r="R363" t="n">
         <v>0.06374613307264126</v>
       </c>
@@ -55229,9 +55079,6 @@
       <c r="O370" t="n">
         <v>46</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0.08885824610125752</v>
       </c>
@@ -56265,9 +56112,6 @@
       <c r="O377" t="n">
         <v>73</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.1410141731606913</v>
       </c>
@@ -57301,9 +57145,6 @@
       <c r="O384" t="n">
         <v>112</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.2163505122465401</v>
       </c>
@@ -58485,9 +58326,6 @@
       <c r="O392" t="n">
         <v>107</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.2066920072355338</v>
       </c>
@@ -59521,9 +59359,6 @@
       <c r="O399" t="n">
         <v>119</v>
       </c>
-      <c r="Q399" t="n">
-        <v>0</v>
-      </c>
       <c r="R399" t="n">
         <v>0.2298724192619488</v>
       </c>
@@ -60557,9 +60392,6 @@
       <c r="O406" t="n">
         <v>160</v>
       </c>
-      <c r="Q406" t="n">
-        <v>0</v>
-      </c>
       <c r="R406" t="n">
         <v>0.3090721603522001</v>
       </c>
@@ -61741,9 +61573,6 @@
       <c r="O414" t="n">
         <v>174</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>0.3361159743830176</v>
       </c>
@@ -62777,9 +62606,6 @@
       <c r="O421" t="n">
         <v>489</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.9446017900764115</v>
       </c>
@@ -63961,9 +63787,6 @@
       <c r="O429" t="n">
         <v>2283</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>4.410073388025455</v>
       </c>
@@ -64996,9 +64819,6 @@
       </c>
       <c r="O436" t="n">
         <v>360</v>
-      </c>
-      <c r="Q436" t="n">
-        <v>0</v>
       </c>
       <c r="R436" t="n">
         <v>0.6954123607924503</v>
